--- a/Data/Barriers.xlsx
+++ b/Data/Barriers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdagostino\Desktop\GITHUB\TRoot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E94DCC00-037F-4055-A288-01F398B716B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF5B94C-6666-439C-B0DC-831A09DED5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C40D24C9-D824-4AEA-ADEF-6030BE4DF8D6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Barrier</t>
   </si>
@@ -87,6 +87,27 @@
   </si>
   <si>
     <t>LC</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>Barrier_Name</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
   </si>
 </sst>
 </file>
@@ -458,13 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8B0C16-4CBE-43CC-8E98-18389422EA06}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +495,11 @@
       <c r="C1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -486,7 +510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -496,8 +520,11 @@
       <c r="C3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -508,7 +535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -518,8 +545,11 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -529,8 +559,11 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -541,7 +574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -551,8 +584,11 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -563,7 +599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -573,8 +609,11 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -583,6 +622,9 @@
       </c>
       <c r="C11" t="s">
         <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
